--- a/dashboard/assets/notas/especial-2022.xlsx
+++ b/dashboard/assets/notas/especial-2022.xlsx
@@ -1,280 +1,42 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>Microsoft Excel</Application>
-  <DocSecurity>0</DocSecurity>
-  <ScaleCrop>false</ScaleCrop>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>Planilhas</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>7</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="7" baseType="lpstr">
-      <vt:lpstr>TOTAL</vt:lpstr>
-      <vt:lpstr>COREOGRAFIA</vt:lpstr>
-      <vt:lpstr>MARCAÇÃO</vt:lpstr>
-      <vt:lpstr>ANIMAÇÃO	</vt:lpstr>
-      <vt:lpstr>FIGURINO</vt:lpstr>
-      <vt:lpstr>CASAL DE NOIVOS	</vt:lpstr>
-      <vt:lpstr>TRILHA SONORA	</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-  <LinksUpToDate>false</LinksUpToDate>
-  <SharedDoc>false</SharedDoc>
-  <HyperlinksChanged>false</HyperlinksChanged>
-  <AppVersion>16.0300</AppVersion>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Documents\GitHub\site-linq-dfe-beta\dashboard\assets\notas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCAB11C-892A-45C6-BF15-39F0B0C038CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="TOTAL" sheetId="7" r:id="rId1"/>
+    <sheet name="COREOGRAFIA" sheetId="1" r:id="rId2"/>
+    <sheet name="MARCAÇÃO" sheetId="2" r:id="rId3"/>
+    <sheet name="ANIMAÇÃO_x0009_" sheetId="3" r:id="rId4"/>
+    <sheet name="FIGURINO" sheetId="4" r:id="rId5"/>
+    <sheet name="CASAL DE NOIVOS_x0009_" sheetId="5" r:id="rId6"/>
+    <sheet name="TRILHA SONORA_x0009_" sheetId="6" r:id="rId7"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <dc:title>aa69d081519554f798a1df0f39fe840ec6ee4595234ae16de1ca3107eb7b9c6f.xlsx</dc:title>
-  <dc:creator>Work4</dc:creator>
-  <cp:lastModifiedBy>Tiago</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-12T20:27:48Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-15T10:59:10Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="Created">
-    <vt:filetime>2026-03-12T00:00:00Z</vt:filetime>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="Creator">
-    <vt:lpwstr>EXCEL.EXE</vt:lpwstr>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="4" name="LastSaved">
-    <vt:filetime>2026-03-12T00:00:00Z</vt:filetime>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="5" name="Producer">
-    <vt:lpwstr>www.ilovepdf.com</vt:lpwstr>
-  </property>
-</Properties>
-</file>
-
-<file path=xl\calcChain.xml><?xml version="1.0" encoding="utf-8"?>
-<calcChain xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <c r="H2" i="7" l="1"/>
-  <c r="I2" i="7" s="1"/>
-  <c r="J2" i="7" s="1"/>
-  <c r="H15" i="6"/>
-  <c r="I15" i="6" s="1"/>
-  <c r="H14" i="6"/>
-  <c r="I14" i="6" s="1"/>
-  <c r="H13" i="6"/>
-  <c r="I13" i="6" s="1"/>
-  <c r="H12" i="6"/>
-  <c r="I12" i="6" s="1"/>
-  <c r="H11" i="6"/>
-  <c r="I11" i="6" s="1"/>
-  <c r="H10" i="6"/>
-  <c r="I10" i="6" s="1"/>
-  <c r="I9" i="6"/>
-  <c r="H9" i="6"/>
-  <c r="H8" i="6"/>
-  <c r="I8" i="6" s="1"/>
-  <c r="H7" i="6"/>
-  <c r="I7" i="6" s="1"/>
-  <c r="H6" i="6"/>
-  <c r="I6" i="6" s="1"/>
-  <c r="H5" i="6"/>
-  <c r="I5" i="6" s="1"/>
-  <c r="H4" i="6"/>
-  <c r="I4" i="6" s="1"/>
-  <c r="H3" i="6"/>
-  <c r="I3" i="6" s="1"/>
-  <c r="H2" i="6"/>
-  <c r="I2" i="6" s="1"/>
-  <c r="H15" i="5"/>
-  <c r="I15" i="5" s="1"/>
-  <c r="H14" i="5"/>
-  <c r="I14" i="5" s="1"/>
-  <c r="H13" i="5"/>
-  <c r="I13" i="5" s="1"/>
-  <c r="H12" i="5"/>
-  <c r="I12" i="5" s="1"/>
-  <c r="H11" i="5"/>
-  <c r="I11" i="5" s="1"/>
-  <c r="H10" i="5"/>
-  <c r="I10" i="5" s="1"/>
-  <c r="H9" i="5"/>
-  <c r="I9" i="5" s="1"/>
-  <c r="H8" i="5"/>
-  <c r="I8" i="5" s="1"/>
-  <c r="H7" i="5"/>
-  <c r="I7" i="5" s="1"/>
-  <c r="H6" i="5"/>
-  <c r="I6" i="5" s="1"/>
-  <c r="H5" i="5"/>
-  <c r="I5" i="5" s="1"/>
-  <c r="H4" i="5"/>
-  <c r="I4" i="5" s="1"/>
-  <c r="H3" i="5"/>
-  <c r="I3" i="5" s="1"/>
-  <c r="H2" i="5"/>
-  <c r="I2" i="5" s="1"/>
-  <c r="H15" i="4"/>
-  <c r="I15" i="4" s="1"/>
-  <c r="H14" i="4"/>
-  <c r="I14" i="4" s="1"/>
-  <c r="H13" i="4"/>
-  <c r="I13" i="4" s="1"/>
-  <c r="H12" i="4"/>
-  <c r="I12" i="4" s="1"/>
-  <c r="H11" i="4"/>
-  <c r="I11" i="4" s="1"/>
-  <c r="H10" i="4"/>
-  <c r="I10" i="4" s="1"/>
-  <c r="H9" i="4"/>
-  <c r="I9" i="4" s="1"/>
-  <c r="H8" i="4"/>
-  <c r="I8" i="4" s="1"/>
-  <c r="H7" i="4"/>
-  <c r="I7" i="4" s="1"/>
-  <c r="H6" i="4"/>
-  <c r="I6" i="4" s="1"/>
-  <c r="H5" i="4"/>
-  <c r="I5" i="4" s="1"/>
-  <c r="H4" i="4"/>
-  <c r="I4" i="4" s="1"/>
-  <c r="H3" i="4"/>
-  <c r="I3" i="4" s="1"/>
-  <c r="H2" i="4"/>
-  <c r="I2" i="4" s="1"/>
-  <c r="H15" i="3"/>
-  <c r="I15" i="3" s="1"/>
-  <c r="H14" i="3"/>
-  <c r="I14" i="3" s="1"/>
-  <c r="H13" i="3"/>
-  <c r="I13" i="3" s="1"/>
-  <c r="H12" i="3"/>
-  <c r="I12" i="3" s="1"/>
-  <c r="H11" i="3"/>
-  <c r="I11" i="3" s="1"/>
-  <c r="H10" i="3"/>
-  <c r="I10" i="3" s="1"/>
-  <c r="H9" i="3"/>
-  <c r="I9" i="3" s="1"/>
-  <c r="H8" i="3"/>
-  <c r="I8" i="3" s="1"/>
-  <c r="H7" i="3"/>
-  <c r="I7" i="3" s="1"/>
-  <c r="H6" i="3"/>
-  <c r="I6" i="3" s="1"/>
-  <c r="H5" i="3"/>
-  <c r="I5" i="3" s="1"/>
-  <c r="H4" i="3"/>
-  <c r="I4" i="3" s="1"/>
-  <c r="H3" i="3"/>
-  <c r="I3" i="3" s="1"/>
-  <c r="H2" i="3"/>
-  <c r="I2" i="3" s="1"/>
-  <c r="H15" i="2"/>
-  <c r="I15" i="2" s="1"/>
-  <c r="H14" i="2"/>
-  <c r="I14" i="2" s="1"/>
-  <c r="H13" i="2"/>
-  <c r="I13" i="2" s="1"/>
-  <c r="H12" i="2"/>
-  <c r="I12" i="2" s="1"/>
-  <c r="H11" i="2"/>
-  <c r="I11" i="2" s="1"/>
-  <c r="H10" i="2"/>
-  <c r="I10" i="2" s="1"/>
-  <c r="H9" i="2"/>
-  <c r="I9" i="2" s="1"/>
-  <c r="H8" i="2"/>
-  <c r="I8" i="2" s="1"/>
-  <c r="H7" i="2"/>
-  <c r="I7" i="2" s="1"/>
-  <c r="H6" i="2"/>
-  <c r="I6" i="2" s="1"/>
-  <c r="H5" i="2"/>
-  <c r="I5" i="2" s="1"/>
-  <c r="H4" i="2"/>
-  <c r="I4" i="2" s="1"/>
-  <c r="H3" i="2"/>
-  <c r="I3" i="2" s="1"/>
-  <c r="H2" i="2"/>
-  <c r="I2" i="2" s="1"/>
-  <c r="H15" i="1"/>
-  <c r="H3" i="1"/>
-  <c r="I3" i="1"/>
-  <c r="H4" i="1"/>
-  <c r="I4" i="1"/>
-  <c r="H5" i="1"/>
-  <c r="I5" i="1" s="1"/>
-  <c r="H6" i="1"/>
-  <c r="I6" i="1"/>
-  <c r="H7" i="1"/>
-  <c r="I7" i="1"/>
-  <c r="H8" i="1"/>
-  <c r="I8" i="1"/>
-  <c r="H9" i="1"/>
-  <c r="I9" i="1" s="1"/>
-  <c r="H10" i="1"/>
-  <c r="I10" i="1"/>
-  <c r="H11" i="1"/>
-  <c r="I11" i="1"/>
-  <c r="H12" i="1"/>
-  <c r="I12" i="1"/>
-  <c r="H13" i="1"/>
-  <c r="I13" i="1" s="1"/>
-  <c r="H14" i="1"/>
-  <c r="I14" i="1"/>
-  <c r="I15" i="1"/>
-  <c r="H2" i="1"/>
-  <c r="I2" i="1" s="1"/>
-  <c r="H15" i="7"/>
-  <c r="H3" i="7"/>
-  <c r="I3" i="7" s="1"/>
-  <c r="J3" i="7" s="1"/>
-  <c r="H4" i="7"/>
-  <c r="I4" i="7" s="1"/>
-  <c r="J4" i="7" s="1"/>
-  <c r="H5" i="7"/>
-  <c r="I5" i="7" s="1"/>
-  <c r="J5" i="7" s="1"/>
-  <c r="H6" i="7"/>
-  <c r="I6" i="7"/>
-  <c r="J6" i="7"/>
-  <c r="H7" i="7"/>
-  <c r="I7" i="7"/>
-  <c r="J7" i="7"/>
-  <c r="H8" i="7"/>
-  <c r="I8" i="7" s="1"/>
-  <c r="J8" i="7" s="1"/>
-  <c r="H9" i="7"/>
-  <c r="I9" i="7"/>
-  <c r="J9" i="7"/>
-  <c r="H10" i="7"/>
-  <c r="I10" i="7"/>
-  <c r="J10" i="7"/>
-  <c r="H11" i="7"/>
-  <c r="I11" i="7" s="1"/>
-  <c r="J11" i="7" s="1"/>
-  <c r="H12" i="7"/>
-  <c r="I12" i="7"/>
-  <c r="J12" i="7"/>
-  <c r="H13" i="7"/>
-  <c r="I13" i="7"/>
-  <c r="J13" i="7" s="1"/>
-  <c r="H14" i="7"/>
-  <c r="I14" i="7"/>
-  <c r="J14" i="7"/>
-  <c r="I15" i="7"/>
-  <c r="J15" i="7"/>
-</calcChain>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="36">
   <si>
     <r>
@@ -600,10 +362,10 @@
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -715,7 +477,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -764,26 +526,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -832,37 +579,31 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -882,7 +623,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1201,44 +942,7 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Documents\GitHub\fantasy-junino\assets\notas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACC961B-124B-471F-BBB6-4A488C6B48FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="TOTAL" sheetId="7" r:id="rId1"/>
-    <sheet name="COREOGRAFIA" sheetId="1" r:id="rId2"/>
-    <sheet name="MARCAÇÃO" sheetId="2" r:id="rId3"/>
-    <sheet name="ANIMAÇÃO_x0009_" sheetId="3" r:id="rId4"/>
-    <sheet name="FIGURINO" sheetId="4" r:id="rId5"/>
-    <sheet name="CASAL DE NOIVOS_x0009_" sheetId="5" r:id="rId6"/>
-    <sheet name="TRILHA SONORA_x0009_" sheetId="6" r:id="rId7"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07150F35-5806-4DA5-8421-042CF59BCCC2}">
   <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="17.83203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -1296,13 +1000,16 @@
         <v>719.3</v>
       </c>
       <c r="H2">
-        <f>G2/COUNTIF(C2:F2,"&lt;&gt;0")</f>
+        <f t="shared" ref="H2:H15" si="0">G2/COUNTIF(C2:F2,"&lt;&gt;0")</f>
+        <v>179.82499999999999</v>
       </c>
       <c r="I2">
-        <f>H2/6</f>
+        <f t="shared" ref="I2:I15" si="1">H2/6</f>
+        <v>29.970833333333331</v>
       </c>
       <c r="J2">
-        <f>I2/3</f>
+        <f t="shared" ref="J2:J15" si="2">I2/3</f>
+        <v>9.9902777777777771</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1328,13 +1035,16 @@
         <v>719</v>
       </c>
       <c r="H3">
-        <f>G3/COUNTIF(C3:F3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>179.75</v>
       </c>
       <c r="I3">
-        <f>H3/6</f>
+        <f t="shared" si="1"/>
+        <v>29.958333333333332</v>
       </c>
       <c r="J3">
-        <f>I3/3</f>
+        <f t="shared" si="2"/>
+        <v>9.9861111111111107</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1360,13 +1070,16 @@
         <v>717.2</v>
       </c>
       <c r="H4">
-        <f>G4/COUNTIF(C4:F4,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>179.3</v>
       </c>
       <c r="I4">
-        <f>H4/6</f>
+        <f t="shared" si="1"/>
+        <v>29.883333333333336</v>
       </c>
       <c r="J4">
-        <f>I4/3</f>
+        <f t="shared" si="2"/>
+        <v>9.9611111111111121</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1376,29 +1089,32 @@
       <c r="B5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="18">
         <v>178.4</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="18">
         <v>179.8</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="18">
         <v>178.6</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="18">
         <v>179.7</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="19">
         <v>716.5</v>
       </c>
       <c r="H5">
-        <f>G5/COUNTIF(C5:F5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>179.125</v>
       </c>
       <c r="I5">
-        <f>H5/6</f>
+        <f t="shared" si="1"/>
+        <v>29.854166666666668</v>
       </c>
       <c r="J5">
-        <f>I5/3</f>
+        <f t="shared" si="2"/>
+        <v>9.9513888888888893</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1408,29 +1124,32 @@
       <c r="B6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="18">
         <v>177.2</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="18">
         <v>178.6</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="18">
         <v>179.8</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="18">
         <v>179.9</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="19">
         <v>715.5</v>
       </c>
       <c r="H6">
-        <f>G6/COUNTIF(C6:F6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>178.875</v>
       </c>
       <c r="I6">
-        <f>H6/6</f>
+        <f t="shared" si="1"/>
+        <v>29.8125</v>
       </c>
       <c r="J6">
-        <f>I6/3</f>
+        <f t="shared" si="2"/>
+        <v>9.9375</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1440,29 +1159,32 @@
       <c r="B7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="18">
         <v>177.1</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="18">
         <v>178.8</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="18">
         <v>178.6</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="18">
         <v>178.8</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="19">
         <v>713.3</v>
       </c>
       <c r="H7">
-        <f>G7/COUNTIF(C7:F7,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>178.32499999999999</v>
       </c>
       <c r="I7">
-        <f>H7/6</f>
+        <f t="shared" si="1"/>
+        <v>29.720833333333331</v>
       </c>
       <c r="J7">
-        <f>I7/3</f>
+        <f t="shared" si="2"/>
+        <v>9.9069444444444432</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1472,29 +1194,32 @@
       <c r="B8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="18">
         <v>177.2</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="18">
         <v>178</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="18">
         <v>178.6</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="18">
         <v>179.2</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="19">
         <v>713</v>
       </c>
       <c r="H8">
-        <f>G8/COUNTIF(C8:F8,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>178.25</v>
       </c>
       <c r="I8">
-        <f>H8/6</f>
+        <f t="shared" si="1"/>
+        <v>29.708333333333332</v>
       </c>
       <c r="J8">
-        <f>I8/3</f>
+        <f t="shared" si="2"/>
+        <v>9.9027777777777768</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1504,29 +1229,32 @@
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="18">
         <v>176.3</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="18">
         <v>177.4</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="18">
         <v>178.9</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="18">
         <v>179</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="19">
         <v>711.6</v>
       </c>
       <c r="H9">
-        <f>G9/COUNTIF(C9:F9,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>177.9</v>
       </c>
       <c r="I9">
-        <f>H9/6</f>
+        <f t="shared" si="1"/>
+        <v>29.650000000000002</v>
       </c>
       <c r="J9">
-        <f>I9/3</f>
+        <f t="shared" si="2"/>
+        <v>9.8833333333333346</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1536,29 +1264,32 @@
       <c r="B10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="18">
         <v>173.8</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="18">
         <v>177.7</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="18">
         <v>179.4</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="18">
         <v>179.8</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="19">
         <v>710.7</v>
       </c>
       <c r="H10">
-        <f>G10/COUNTIF(C10:F10,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>177.67500000000001</v>
       </c>
       <c r="I10">
-        <f>H10/6</f>
+        <f t="shared" si="1"/>
+        <v>29.612500000000001</v>
       </c>
       <c r="J10">
-        <f>I10/3</f>
+        <f t="shared" si="2"/>
+        <v>9.8708333333333336</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -1568,29 +1299,32 @@
       <c r="B11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="18">
         <v>173.9</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="18">
         <v>177.4</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="18">
         <v>179.4</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="18">
         <v>179.1</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="19">
         <v>709.8</v>
       </c>
       <c r="H11">
-        <f>G11/COUNTIF(C11:F11,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>177.45</v>
       </c>
       <c r="I11">
-        <f>H11/6</f>
+        <f t="shared" si="1"/>
+        <v>29.574999999999999</v>
       </c>
       <c r="J11">
-        <f>I11/3</f>
+        <f t="shared" si="2"/>
+        <v>9.8583333333333325</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -1600,29 +1334,32 @@
       <c r="B12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="18">
         <v>172.2</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="18">
         <v>177.8</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="18">
         <v>178.8</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="18">
         <v>179.7</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="19">
         <v>708.5</v>
       </c>
       <c r="H12">
-        <f>G12/COUNTIF(C12:F12,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>177.125</v>
       </c>
       <c r="I12">
-        <f>H12/6</f>
+        <f t="shared" si="1"/>
+        <v>29.520833333333332</v>
       </c>
       <c r="J12">
-        <f>I12/3</f>
+        <f t="shared" si="2"/>
+        <v>9.8402777777777768</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -1632,29 +1369,32 @@
       <c r="B13" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="18">
         <v>175.8</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="18">
         <v>175.3</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="18">
         <v>179</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="18">
         <v>176.6</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="19">
         <v>706.7</v>
       </c>
       <c r="H13">
-        <f>G13/COUNTIF(C13:F13,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>176.67500000000001</v>
       </c>
       <c r="I13">
-        <f>H13/6</f>
+        <f t="shared" si="1"/>
+        <v>29.445833333333336</v>
       </c>
       <c r="J13">
-        <f>I13/3</f>
+        <f t="shared" si="2"/>
+        <v>9.8152777777777782</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1664,29 +1404,32 @@
       <c r="B14" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="20">
         <v>172.9</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="20">
         <v>170.5</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="20">
         <v>177.2</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="20">
         <v>178.2</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="21">
         <v>698.8</v>
       </c>
       <c r="H14">
-        <f>G14/COUNTIF(C14:F14,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>174.7</v>
       </c>
       <c r="I14">
-        <f>H14/6</f>
+        <f t="shared" si="1"/>
+        <v>29.116666666666664</v>
       </c>
       <c r="J14">
-        <f>I14/3</f>
+        <f t="shared" si="2"/>
+        <v>9.7055555555555539</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1696,29 +1439,32 @@
       <c r="B15" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="20">
         <v>176</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="20">
         <v>174.6</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="20">
         <v>179.5</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="20">
         <v>0</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="21">
         <v>530.1</v>
       </c>
       <c r="H15">
-        <f>G15/COUNTIF(C15:F15,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>176.70000000000002</v>
       </c>
       <c r="I15">
-        <f>H15/6</f>
+        <f t="shared" si="1"/>
+        <v>29.450000000000003</v>
       </c>
       <c r="J15">
-        <f>I15/3</f>
+        <f t="shared" si="2"/>
+        <v>9.8166666666666682</v>
       </c>
     </row>
   </sheetData>
@@ -1727,7 +1473,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -1769,26 +1515,28 @@
       <c r="B2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="24">
+      <c r="C2" s="22">
         <v>29.8</v>
       </c>
-      <c r="D2" s="24">
-        <v>30</v>
-      </c>
-      <c r="E2" s="24">
+      <c r="D2" s="22">
+        <v>30</v>
+      </c>
+      <c r="E2" s="22">
         <v>29.8</v>
       </c>
-      <c r="F2" s="24">
-        <v>30</v>
-      </c>
-      <c r="G2" s="25">
+      <c r="F2" s="22">
+        <v>30</v>
+      </c>
+      <c r="G2" s="23">
         <v>119.6</v>
       </c>
       <c r="H2">
-        <f>G2/COUNTIF(C2:F2,"&lt;&gt;0")</f>
+        <f t="shared" ref="H2:H15" si="0">G2/COUNTIF(C2:F2,"&lt;&gt;0")</f>
+        <v>29.9</v>
       </c>
       <c r="I2">
-        <f>H2/3</f>
+        <f t="shared" ref="I2:I15" si="1">H2/3</f>
+        <v>9.9666666666666668</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1798,26 +1546,28 @@
       <c r="B3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="24">
         <v>29.7</v>
       </c>
-      <c r="D3" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="E3" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F3" s="26">
-        <v>30</v>
-      </c>
-      <c r="G3" s="20">
+      <c r="D3" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="E3" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F3" s="24">
+        <v>30</v>
+      </c>
+      <c r="G3" s="18">
         <v>119.5</v>
       </c>
       <c r="H3">
-        <f>G3/COUNTIF(C3:F3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.875</v>
       </c>
       <c r="I3">
-        <f>H3/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9583333333333339</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1827,26 +1577,28 @@
       <c r="B4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="24">
         <v>29.5</v>
       </c>
-      <c r="D4" s="26">
-        <v>30</v>
-      </c>
-      <c r="E4" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F4" s="26">
-        <v>30</v>
-      </c>
-      <c r="G4" s="20">
+      <c r="D4" s="24">
+        <v>30</v>
+      </c>
+      <c r="E4" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F4" s="24">
+        <v>30</v>
+      </c>
+      <c r="G4" s="18">
         <v>119.4</v>
       </c>
       <c r="H4">
-        <f>G4/COUNTIF(C4:F4,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.85</v>
       </c>
       <c r="I4">
-        <f>H4/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9500000000000011</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1856,26 +1608,28 @@
       <c r="B5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="24">
         <v>29.4</v>
       </c>
-      <c r="D5" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="E5" s="26">
-        <v>30</v>
-      </c>
-      <c r="F5" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="G5" s="20">
+      <c r="D5" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="E5" s="24">
+        <v>30</v>
+      </c>
+      <c r="F5" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="G5" s="18">
         <v>119.2</v>
       </c>
       <c r="H5">
-        <f>G5/COUNTIF(C5:F5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.8</v>
       </c>
       <c r="I5">
-        <f>H5/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9333333333333336</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1885,26 +1639,28 @@
       <c r="B6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="24">
         <v>29.6</v>
       </c>
-      <c r="D6" s="26">
-        <v>30</v>
-      </c>
-      <c r="E6" s="26">
+      <c r="D6" s="24">
+        <v>30</v>
+      </c>
+      <c r="E6" s="24">
         <v>29.4</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="24">
         <v>29.8</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="18">
         <v>118.8</v>
       </c>
       <c r="H6">
-        <f>G6/COUNTIF(C6:F6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.7</v>
       </c>
       <c r="I6">
-        <f>H6/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1914,26 +1670,28 @@
       <c r="B7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="24">
         <v>29.4</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="24">
         <v>29.8</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="24">
         <v>29.3</v>
       </c>
-      <c r="F7" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="G7" s="20">
+      <c r="F7" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="G7" s="18">
         <v>118.4</v>
       </c>
       <c r="H7">
-        <f>G7/COUNTIF(C7:F7,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.6</v>
       </c>
       <c r="I7">
-        <f>H7/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8666666666666671</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1943,26 +1701,28 @@
       <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="24">
         <v>29.2</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="24">
         <v>29.6</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="24">
         <v>29.6</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="24">
         <v>29.5</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="18">
         <v>117.9</v>
       </c>
       <c r="H8">
-        <f>G8/COUNTIF(C8:F8,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.475000000000001</v>
       </c>
       <c r="I8">
-        <f>H8/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8250000000000011</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1972,26 +1732,28 @@
       <c r="B9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="24">
         <v>29</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="24">
         <v>29.3</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="24">
         <v>29.7</v>
       </c>
-      <c r="F9" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="G9" s="20">
+      <c r="F9" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="G9" s="18">
         <v>117.9</v>
       </c>
       <c r="H9">
-        <f>G9/COUNTIF(C9:F9,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.475000000000001</v>
       </c>
       <c r="I9">
-        <f>H9/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8250000000000011</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2001,26 +1763,28 @@
       <c r="B10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="24">
         <v>29.3</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="24">
         <v>29.6</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="24">
         <v>29.4</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="24">
         <v>29.6</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="18">
         <v>117.9</v>
       </c>
       <c r="H10">
-        <f>G10/COUNTIF(C10:F10,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.475000000000001</v>
       </c>
       <c r="I10">
-        <f>H10/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8250000000000011</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2030,26 +1794,28 @@
       <c r="B11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="24">
         <v>28.9</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="24">
         <v>29.4</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="24">
         <v>29.6</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="24">
         <v>29.5</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="18">
         <v>117.4</v>
       </c>
       <c r="H11">
-        <f>G11/COUNTIF(C11:F11,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.35</v>
       </c>
       <c r="I11">
-        <f>H11/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7833333333333332</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2059,26 +1825,28 @@
       <c r="B12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="24">
         <v>28.7</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="24">
         <v>29.4</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="24">
         <v>29.4</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="24">
         <v>29.8</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="18">
         <v>117.3</v>
       </c>
       <c r="H12">
-        <f>G12/COUNTIF(C12:F12,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.324999999999999</v>
       </c>
       <c r="I12">
-        <f>H12/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7750000000000004</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2088,26 +1856,28 @@
       <c r="B13" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="24">
         <v>29.3</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="24">
         <v>28.9</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="24">
         <v>29.6</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="24">
         <v>29.2</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="18">
         <v>117</v>
       </c>
       <c r="H13">
-        <f>G13/COUNTIF(C13:F13,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.25</v>
       </c>
       <c r="I13">
-        <f>H13/3</f>
+        <f t="shared" si="1"/>
+        <v>9.75</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2117,26 +1887,28 @@
       <c r="B14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="24">
         <v>28.3</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="24">
         <v>29</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="24">
         <v>29.1</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="24">
         <v>29.2</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="18">
         <v>115.6</v>
       </c>
       <c r="H14">
-        <f>G14/COUNTIF(C14:F14,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>28.9</v>
       </c>
       <c r="I14">
-        <f>H14/3</f>
+        <f t="shared" si="1"/>
+        <v>9.6333333333333329</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2146,26 +1918,28 @@
       <c r="B15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="24">
         <v>29.2</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="24">
         <v>28.5</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="24">
         <v>29.6</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="24">
         <v>0</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="18">
         <v>87.3</v>
       </c>
       <c r="H15">
-        <f>G15/COUNTIF(C15:F15,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.099999999999998</v>
       </c>
       <c r="I15">
-        <f>H15/3</f>
+        <f t="shared" si="1"/>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2188,7 +1962,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -2230,26 +2004,28 @@
       <c r="B2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24">
-        <v>29.9</v>
-      </c>
-      <c r="D2" s="24">
-        <v>30</v>
-      </c>
-      <c r="E2" s="24">
-        <v>30</v>
-      </c>
-      <c r="F2" s="24">
-        <v>30</v>
-      </c>
-      <c r="G2" s="25">
+      <c r="C2" s="22">
+        <v>29.9</v>
+      </c>
+      <c r="D2" s="22">
+        <v>30</v>
+      </c>
+      <c r="E2" s="22">
+        <v>30</v>
+      </c>
+      <c r="F2" s="22">
+        <v>30</v>
+      </c>
+      <c r="G2" s="23">
         <v>119.9</v>
       </c>
       <c r="H2">
-        <f>G2/COUNTIF(C2:F2,"&lt;&gt;0")</f>
+        <f t="shared" ref="H2:H15" si="0">G2/COUNTIF(C2:F2,"&lt;&gt;0")</f>
+        <v>29.975000000000001</v>
       </c>
       <c r="I2">
-        <f>H2/3</f>
+        <f t="shared" ref="I2:I15" si="1">H2/3</f>
+        <v>9.9916666666666671</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2257,26 +2033,28 @@
       <c r="B3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="D3" s="26">
-        <v>30</v>
-      </c>
-      <c r="E3" s="26">
-        <v>30</v>
-      </c>
-      <c r="F3" s="26">
-        <v>30</v>
-      </c>
-      <c r="G3" s="20">
+      <c r="C3" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="D3" s="24">
+        <v>30</v>
+      </c>
+      <c r="E3" s="24">
+        <v>30</v>
+      </c>
+      <c r="F3" s="24">
+        <v>30</v>
+      </c>
+      <c r="G3" s="18">
         <v>119.9</v>
       </c>
       <c r="H3">
-        <f>G3/COUNTIF(C3:F3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.975000000000001</v>
       </c>
       <c r="I3">
-        <f>H3/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9916666666666671</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2286,26 +2064,28 @@
       <c r="B4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="24">
         <v>29.8</v>
       </c>
-      <c r="D4" s="26">
-        <v>30</v>
-      </c>
-      <c r="E4" s="26">
-        <v>30</v>
-      </c>
-      <c r="F4" s="26">
-        <v>30</v>
-      </c>
-      <c r="G4" s="20">
+      <c r="D4" s="24">
+        <v>30</v>
+      </c>
+      <c r="E4" s="24">
+        <v>30</v>
+      </c>
+      <c r="F4" s="24">
+        <v>30</v>
+      </c>
+      <c r="G4" s="18">
         <v>119.8</v>
       </c>
       <c r="H4">
-        <f>G4/COUNTIF(C4:F4,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.95</v>
       </c>
       <c r="I4">
-        <f>H4/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9833333333333325</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2315,26 +2095,28 @@
       <c r="B5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="24">
         <v>29.7</v>
       </c>
-      <c r="D5" s="26">
-        <v>30</v>
-      </c>
-      <c r="E5" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F5" s="26">
-        <v>30</v>
-      </c>
-      <c r="G5" s="20">
+      <c r="D5" s="24">
+        <v>30</v>
+      </c>
+      <c r="E5" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F5" s="24">
+        <v>30</v>
+      </c>
+      <c r="G5" s="18">
         <v>119.6</v>
       </c>
       <c r="H5">
-        <f>G5/COUNTIF(C5:F5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.9</v>
       </c>
       <c r="I5">
-        <f>H5/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9666666666666668</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2344,26 +2126,28 @@
       <c r="B6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="24">
         <v>29.6</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="24">
         <v>29.8</v>
       </c>
-      <c r="E6" s="26">
-        <v>30</v>
-      </c>
-      <c r="F6" s="26">
-        <v>30</v>
-      </c>
-      <c r="G6" s="20">
+      <c r="E6" s="24">
+        <v>30</v>
+      </c>
+      <c r="F6" s="24">
+        <v>30</v>
+      </c>
+      <c r="G6" s="18">
         <v>119.4</v>
       </c>
       <c r="H6">
-        <f>G6/COUNTIF(C6:F6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.85</v>
       </c>
       <c r="I6">
-        <f>H6/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9500000000000011</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2373,26 +2157,28 @@
       <c r="B7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="24">
         <v>29.2</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="24">
         <v>29.6</v>
       </c>
-      <c r="E7" s="26">
-        <v>30</v>
-      </c>
-      <c r="F7" s="26">
-        <v>30</v>
-      </c>
-      <c r="G7" s="20">
+      <c r="E7" s="24">
+        <v>30</v>
+      </c>
+      <c r="F7" s="24">
+        <v>30</v>
+      </c>
+      <c r="G7" s="18">
         <v>118.8</v>
       </c>
       <c r="H7">
-        <f>G7/COUNTIF(C7:F7,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.7</v>
       </c>
       <c r="I7">
-        <f>H7/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2402,26 +2188,28 @@
       <c r="B8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="24">
         <v>29.5</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="24">
         <v>29.8</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="24">
         <v>29.5</v>
       </c>
-      <c r="F8" s="26">
-        <v>30</v>
-      </c>
-      <c r="G8" s="20">
+      <c r="F8" s="24">
+        <v>30</v>
+      </c>
+      <c r="G8" s="18">
         <v>118.8</v>
       </c>
       <c r="H8">
-        <f>G8/COUNTIF(C8:F8,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.7</v>
       </c>
       <c r="I8">
-        <f>H8/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2431,26 +2219,28 @@
       <c r="B9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="24">
         <v>29</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="24">
         <v>29.6</v>
       </c>
-      <c r="E9" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F9" s="26">
-        <v>30</v>
-      </c>
-      <c r="G9" s="20">
+      <c r="E9" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F9" s="24">
+        <v>30</v>
+      </c>
+      <c r="G9" s="18">
         <v>118.5</v>
       </c>
       <c r="H9">
-        <f>G9/COUNTIF(C9:F9,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.625</v>
       </c>
       <c r="I9">
-        <f>H9/3</f>
+        <f t="shared" si="1"/>
+        <v>9.875</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2460,26 +2250,28 @@
       <c r="B10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="24">
         <v>28.8</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="24">
         <v>29.6</v>
       </c>
-      <c r="E10" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F10" s="26">
-        <v>30</v>
-      </c>
-      <c r="G10" s="20">
+      <c r="E10" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F10" s="24">
+        <v>30</v>
+      </c>
+      <c r="G10" s="18">
         <v>118.3</v>
       </c>
       <c r="H10">
-        <f>G10/COUNTIF(C10:F10,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.574999999999999</v>
       </c>
       <c r="I10">
-        <f>H10/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8583333333333325</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2489,26 +2281,28 @@
       <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="24">
         <v>29</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="24">
         <v>29.3</v>
       </c>
-      <c r="E11" s="26">
-        <v>30</v>
-      </c>
-      <c r="F11" s="26">
-        <v>30</v>
-      </c>
-      <c r="G11" s="20">
+      <c r="E11" s="24">
+        <v>30</v>
+      </c>
+      <c r="F11" s="24">
+        <v>30</v>
+      </c>
+      <c r="G11" s="18">
         <v>118.3</v>
       </c>
       <c r="H11">
-        <f>G11/COUNTIF(C11:F11,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.574999999999999</v>
       </c>
       <c r="I11">
-        <f>H11/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8583333333333325</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2518,26 +2312,28 @@
       <c r="B12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="24">
         <v>28.9</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="24">
         <v>29.4</v>
       </c>
-      <c r="E12" s="26">
-        <v>30</v>
-      </c>
-      <c r="F12" s="26">
-        <v>30</v>
-      </c>
-      <c r="G12" s="20">
+      <c r="E12" s="24">
+        <v>30</v>
+      </c>
+      <c r="F12" s="24">
+        <v>30</v>
+      </c>
+      <c r="G12" s="18">
         <v>118.3</v>
       </c>
       <c r="H12">
-        <f>G12/COUNTIF(C12:F12,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.574999999999999</v>
       </c>
       <c r="I12">
-        <f>H12/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8583333333333325</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2547,26 +2343,28 @@
       <c r="B13" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="24">
         <v>28.6</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="24">
         <v>29.2</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="24">
         <v>29.5</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="24">
         <v>29.8</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="18">
         <v>117.1</v>
       </c>
       <c r="H13">
-        <f>G13/COUNTIF(C13:F13,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.274999999999999</v>
       </c>
       <c r="I13">
-        <f>H13/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7583333333333329</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2576,26 +2374,28 @@
       <c r="B14" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="24">
         <v>28.8</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="24">
         <v>29.4</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="24">
         <v>29.8</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="24">
         <v>29.1</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="18">
         <v>117.1</v>
       </c>
       <c r="H14">
-        <f>G14/COUNTIF(C14:F14,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.274999999999999</v>
       </c>
       <c r="I14">
-        <f>H14/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7583333333333329</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2605,26 +2405,28 @@
       <c r="B15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="24">
         <v>29.5</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="24">
         <v>29.4</v>
       </c>
-      <c r="E15" s="26">
-        <v>30</v>
-      </c>
-      <c r="F15" s="26">
+      <c r="E15" s="24">
+        <v>30</v>
+      </c>
+      <c r="F15" s="24">
         <v>0</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="18">
         <v>88.9</v>
       </c>
       <c r="H15">
-        <f>G15/COUNTIF(C15:F15,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.633333333333336</v>
       </c>
       <c r="I15">
-        <f>H15/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8777777777777782</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2647,7 +2449,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -2690,26 +2492,28 @@
       <c r="B2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="24">
-        <v>30</v>
-      </c>
-      <c r="D2" s="24">
-        <v>30</v>
-      </c>
-      <c r="E2" s="24">
-        <v>30</v>
-      </c>
-      <c r="F2" s="24">
-        <v>30</v>
-      </c>
-      <c r="G2" s="25">
+      <c r="C2" s="22">
+        <v>30</v>
+      </c>
+      <c r="D2" s="22">
+        <v>30</v>
+      </c>
+      <c r="E2" s="22">
+        <v>30</v>
+      </c>
+      <c r="F2" s="22">
+        <v>30</v>
+      </c>
+      <c r="G2" s="23">
         <v>120</v>
       </c>
       <c r="H2">
-        <f>G2/COUNTIF(C2:F2,"&lt;&gt;0")</f>
+        <f t="shared" ref="H2:H15" si="0">G2/COUNTIF(C2:F2,"&lt;&gt;0")</f>
+        <v>30</v>
       </c>
       <c r="I2">
-        <f>H2/3</f>
+        <f t="shared" ref="I2:I15" si="1">H2/3</f>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2717,26 +2521,28 @@
       <c r="B3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="26">
-        <v>30</v>
-      </c>
-      <c r="D3" s="26">
-        <v>30</v>
-      </c>
-      <c r="E3" s="26">
-        <v>30</v>
-      </c>
-      <c r="F3" s="26">
-        <v>30</v>
-      </c>
-      <c r="G3" s="20">
+      <c r="C3" s="24">
+        <v>30</v>
+      </c>
+      <c r="D3" s="24">
+        <v>30</v>
+      </c>
+      <c r="E3" s="24">
+        <v>30</v>
+      </c>
+      <c r="F3" s="24">
+        <v>30</v>
+      </c>
+      <c r="G3" s="18">
         <v>120</v>
       </c>
       <c r="H3">
-        <f>G3/COUNTIF(C3:F3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="I3">
-        <f>H3/3</f>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2746,26 +2552,28 @@
       <c r="B4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="D4" s="26">
-        <v>30</v>
-      </c>
-      <c r="E4" s="26">
-        <v>30</v>
-      </c>
-      <c r="F4" s="26">
-        <v>30</v>
-      </c>
-      <c r="G4" s="20">
+      <c r="C4" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="D4" s="24">
+        <v>30</v>
+      </c>
+      <c r="E4" s="24">
+        <v>30</v>
+      </c>
+      <c r="F4" s="24">
+        <v>30</v>
+      </c>
+      <c r="G4" s="18">
         <v>119.9</v>
       </c>
       <c r="H4">
-        <f>G4/COUNTIF(C4:F4,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.975000000000001</v>
       </c>
       <c r="I4">
-        <f>H4/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9916666666666671</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2775,26 +2583,28 @@
       <c r="B5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="24">
         <v>29.8</v>
       </c>
-      <c r="D5" s="26">
-        <v>30</v>
-      </c>
-      <c r="E5" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F5" s="26">
-        <v>30</v>
-      </c>
-      <c r="G5" s="20">
+      <c r="D5" s="24">
+        <v>30</v>
+      </c>
+      <c r="E5" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F5" s="24">
+        <v>30</v>
+      </c>
+      <c r="G5" s="18">
         <v>119.7</v>
       </c>
       <c r="H5">
-        <f>G5/COUNTIF(C5:F5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.925000000000001</v>
       </c>
       <c r="I5">
-        <f>H5/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9749999999999996</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2804,26 +2614,28 @@
       <c r="B6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="24">
         <v>29.7</v>
       </c>
-      <c r="D6" s="26">
-        <v>30</v>
-      </c>
-      <c r="E6" s="26">
+      <c r="D6" s="24">
+        <v>30</v>
+      </c>
+      <c r="E6" s="24">
         <v>29.8</v>
       </c>
-      <c r="F6" s="26">
-        <v>30</v>
-      </c>
-      <c r="G6" s="20">
+      <c r="F6" s="24">
+        <v>30</v>
+      </c>
+      <c r="G6" s="18">
         <v>119.5</v>
       </c>
       <c r="H6">
-        <f>G6/COUNTIF(C6:F6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.875</v>
       </c>
       <c r="I6">
-        <f>H6/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9583333333333339</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2833,26 +2645,28 @@
       <c r="B7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="24">
         <v>29.4</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="24">
         <v>29.6</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="24">
         <v>29.8</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="24">
         <v>29.8</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="18">
         <v>118.6</v>
       </c>
       <c r="H7">
-        <f>G7/COUNTIF(C7:F7,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.65</v>
       </c>
       <c r="I7">
-        <f>H7/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8833333333333329</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2862,26 +2676,28 @@
       <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="24">
         <v>29.1</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="24">
         <v>29.6</v>
       </c>
-      <c r="E8" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F8" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="G8" s="20">
+      <c r="E8" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F8" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="G8" s="18">
         <v>118.5</v>
       </c>
       <c r="H8">
-        <f>G8/COUNTIF(C8:F8,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.625</v>
       </c>
       <c r="I8">
-        <f>H8/3</f>
+        <f t="shared" si="1"/>
+        <v>9.875</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2891,26 +2707,28 @@
       <c r="B9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="24">
         <v>29.3</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="24">
         <v>29.7</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="24">
         <v>29.8</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="24">
         <v>29.6</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="18">
         <v>118.4</v>
       </c>
       <c r="H9">
-        <f>G9/COUNTIF(C9:F9,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.6</v>
       </c>
       <c r="I9">
-        <f>H9/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8666666666666671</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2920,26 +2738,28 @@
       <c r="B10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="24">
         <v>28.6</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="24">
         <v>29.8</v>
       </c>
-      <c r="E10" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F10" s="26">
-        <v>30</v>
-      </c>
-      <c r="G10" s="20">
+      <c r="E10" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F10" s="24">
+        <v>30</v>
+      </c>
+      <c r="G10" s="18">
         <v>118.3</v>
       </c>
       <c r="H10">
-        <f>G10/COUNTIF(C10:F10,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.574999999999999</v>
       </c>
       <c r="I10">
-        <f>H10/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8583333333333325</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2949,26 +2769,28 @@
       <c r="B11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="24">
         <v>28.8</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="24">
         <v>29.6</v>
       </c>
-      <c r="E11" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F11" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="G11" s="20">
+      <c r="E11" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F11" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="G11" s="18">
         <v>118.2</v>
       </c>
       <c r="H11">
-        <f>G11/COUNTIF(C11:F11,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.55</v>
       </c>
       <c r="I11">
-        <f>H11/3</f>
+        <f t="shared" si="1"/>
+        <v>9.85</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2978,26 +2800,28 @@
       <c r="B12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="24">
         <v>28.6</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="24">
         <v>29.4</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="24">
         <v>29.8</v>
       </c>
-      <c r="F12" s="26">
-        <v>30</v>
-      </c>
-      <c r="G12" s="20">
+      <c r="F12" s="24">
+        <v>30</v>
+      </c>
+      <c r="G12" s="18">
         <v>117.8</v>
       </c>
       <c r="H12">
-        <f>G12/COUNTIF(C12:F12,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.45</v>
       </c>
       <c r="I12">
-        <f>H12/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8166666666666664</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3007,26 +2831,28 @@
       <c r="B13" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="24">
         <v>28.7</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="24">
         <v>29</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="24">
         <v>29.6</v>
       </c>
-      <c r="F13" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="G13" s="20">
+      <c r="F13" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="G13" s="18">
         <v>117.2</v>
       </c>
       <c r="H13">
-        <f>G13/COUNTIF(C13:F13,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.3</v>
       </c>
       <c r="I13">
-        <f>H13/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7666666666666675</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3036,26 +2862,28 @@
       <c r="B14" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="24">
         <v>29</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="24">
         <v>29.1</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="24">
         <v>29.8</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="24">
         <v>29.3</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="18">
         <v>117.2</v>
       </c>
       <c r="H14">
-        <f>G14/COUNTIF(C14:F14,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.3</v>
       </c>
       <c r="I14">
-        <f>H14/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7666666666666675</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3065,26 +2893,28 @@
       <c r="B15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="24">
         <v>29</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="24">
         <v>28.8</v>
       </c>
-      <c r="E15" s="26">
-        <v>30</v>
-      </c>
-      <c r="F15" s="26">
+      <c r="E15" s="24">
+        <v>30</v>
+      </c>
+      <c r="F15" s="24">
         <v>0</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="18">
         <v>87.8</v>
       </c>
       <c r="H15">
-        <f>G15/COUNTIF(C15:F15,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.266666666666666</v>
       </c>
       <c r="I15">
-        <f>H15/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7555555555555546</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3107,7 +2937,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -3150,26 +2980,28 @@
       <c r="B2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="24">
-        <v>30</v>
-      </c>
-      <c r="D2" s="24">
-        <v>30</v>
-      </c>
-      <c r="E2" s="24">
-        <v>30</v>
-      </c>
-      <c r="F2" s="24">
-        <v>30</v>
-      </c>
-      <c r="G2" s="25">
+      <c r="C2" s="22">
+        <v>30</v>
+      </c>
+      <c r="D2" s="22">
+        <v>30</v>
+      </c>
+      <c r="E2" s="22">
+        <v>30</v>
+      </c>
+      <c r="F2" s="22">
+        <v>30</v>
+      </c>
+      <c r="G2" s="23">
         <v>120</v>
       </c>
       <c r="H2">
-        <f>G2/COUNTIF(C2:F2,"&lt;&gt;0")</f>
+        <f t="shared" ref="H2:H15" si="0">G2/COUNTIF(C2:F2,"&lt;&gt;0")</f>
+        <v>30</v>
       </c>
       <c r="I2">
-        <f>H2/3</f>
+        <f t="shared" ref="I2:I15" si="1">H2/3</f>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3179,26 +3011,28 @@
       <c r="B3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="D3" s="26">
-        <v>30</v>
-      </c>
-      <c r="E3" s="26">
-        <v>30</v>
-      </c>
-      <c r="F3" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="G3" s="20">
+      <c r="C3" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="D3" s="24">
+        <v>30</v>
+      </c>
+      <c r="E3" s="24">
+        <v>30</v>
+      </c>
+      <c r="F3" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="G3" s="18">
         <v>119.8</v>
       </c>
       <c r="H3">
-        <f>G3/COUNTIF(C3:F3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.95</v>
       </c>
       <c r="I3">
-        <f>H3/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9833333333333325</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3208,26 +3042,28 @@
       <c r="B4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="26">
-        <v>30</v>
-      </c>
-      <c r="D4" s="26">
+      <c r="C4" s="24">
+        <v>30</v>
+      </c>
+      <c r="D4" s="24">
         <v>29.6</v>
       </c>
-      <c r="E4" s="26">
-        <v>30</v>
-      </c>
-      <c r="F4" s="26">
-        <v>30</v>
-      </c>
-      <c r="G4" s="20">
+      <c r="E4" s="24">
+        <v>30</v>
+      </c>
+      <c r="F4" s="24">
+        <v>30</v>
+      </c>
+      <c r="G4" s="18">
         <v>119.6</v>
       </c>
       <c r="H4">
-        <f>G4/COUNTIF(C4:F4,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.9</v>
       </c>
       <c r="I4">
-        <f>H4/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9666666666666668</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3237,26 +3073,28 @@
       <c r="B5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="24">
         <v>29.6</v>
       </c>
-      <c r="D5" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="E5" s="26">
-        <v>30</v>
-      </c>
-      <c r="F5" s="26">
-        <v>30</v>
-      </c>
-      <c r="G5" s="20">
+      <c r="D5" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="E5" s="24">
+        <v>30</v>
+      </c>
+      <c r="F5" s="24">
+        <v>30</v>
+      </c>
+      <c r="G5" s="18">
         <v>119.5</v>
       </c>
       <c r="H5">
-        <f>G5/COUNTIF(C5:F5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.875</v>
       </c>
       <c r="I5">
-        <f>H5/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9583333333333339</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3266,26 +3104,28 @@
       <c r="B6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="24">
         <v>29.8</v>
       </c>
-      <c r="D6" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="E6" s="26">
+      <c r="D6" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="E6" s="24">
         <v>29.7</v>
       </c>
-      <c r="F6" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="G6" s="20">
+      <c r="F6" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="G6" s="18">
         <v>119.3</v>
       </c>
       <c r="H6">
-        <f>G6/COUNTIF(C6:F6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.824999999999999</v>
       </c>
       <c r="I6">
-        <f>H6/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9416666666666664</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3295,26 +3135,28 @@
       <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="24">
         <v>29.3</v>
       </c>
-      <c r="D7" s="26">
-        <v>30</v>
-      </c>
-      <c r="E7" s="26">
-        <v>30</v>
-      </c>
-      <c r="F7" s="26">
-        <v>30</v>
-      </c>
-      <c r="G7" s="20">
+      <c r="D7" s="24">
+        <v>30</v>
+      </c>
+      <c r="E7" s="24">
+        <v>30</v>
+      </c>
+      <c r="F7" s="24">
+        <v>30</v>
+      </c>
+      <c r="G7" s="18">
         <v>119.3</v>
       </c>
       <c r="H7">
-        <f>G7/COUNTIF(C7:F7,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.824999999999999</v>
       </c>
       <c r="I7">
-        <f>H7/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9416666666666664</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3324,26 +3166,28 @@
       <c r="B8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="24">
         <v>29.6</v>
       </c>
-      <c r="D8" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="E8" s="26">
-        <v>30</v>
-      </c>
-      <c r="F8" s="26">
+      <c r="D8" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="E8" s="24">
+        <v>30</v>
+      </c>
+      <c r="F8" s="24">
         <v>29.8</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="18">
         <v>119.3</v>
       </c>
       <c r="H8">
-        <f>G8/COUNTIF(C8:F8,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.824999999999999</v>
       </c>
       <c r="I8">
-        <f>H8/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9416666666666664</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3353,26 +3197,28 @@
       <c r="B9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="24">
         <v>29.6</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="24">
         <v>29.6</v>
       </c>
-      <c r="E9" s="26">
-        <v>30</v>
-      </c>
-      <c r="F9" s="26">
-        <v>30</v>
-      </c>
-      <c r="G9" s="20">
+      <c r="E9" s="24">
+        <v>30</v>
+      </c>
+      <c r="F9" s="24">
+        <v>30</v>
+      </c>
+      <c r="G9" s="18">
         <v>119.2</v>
       </c>
       <c r="H9">
-        <f>G9/COUNTIF(C9:F9,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.8</v>
       </c>
       <c r="I9">
-        <f>H9/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9333333333333336</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3382,26 +3228,28 @@
       <c r="B10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="24">
         <v>29.7</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="24">
         <v>29.6</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="24">
         <v>29.8</v>
       </c>
-      <c r="F10" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="G10" s="20">
+      <c r="F10" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="G10" s="18">
         <v>119</v>
       </c>
       <c r="H10">
-        <f>G10/COUNTIF(C10:F10,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.75</v>
       </c>
       <c r="I10">
-        <f>H10/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9166666666666661</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3411,26 +3259,28 @@
       <c r="B11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="24">
         <v>29.7</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="24">
         <v>29.5</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="24">
         <v>29.7</v>
       </c>
-      <c r="F11" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="G11" s="20">
+      <c r="F11" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="G11" s="18">
         <v>118.8</v>
       </c>
       <c r="H11">
-        <f>G11/COUNTIF(C11:F11,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.7</v>
       </c>
       <c r="I11">
-        <f>H11/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3440,26 +3290,28 @@
       <c r="B12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="24">
         <v>29.8</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="24">
         <v>29.1</v>
       </c>
-      <c r="E12" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F12" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="G12" s="20">
+      <c r="E12" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F12" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="G12" s="18">
         <v>118.7</v>
       </c>
       <c r="H12">
-        <f>G12/COUNTIF(C12:F12,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.675000000000001</v>
       </c>
       <c r="I12">
-        <f>H12/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8916666666666675</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3469,26 +3321,28 @@
       <c r="B13" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="24">
         <v>29.2</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="24">
         <v>29.8</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="24">
         <v>29.8</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="24">
         <v>29.6</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="18">
         <v>118.4</v>
       </c>
       <c r="H13">
-        <f>G13/COUNTIF(C13:F13,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.6</v>
       </c>
       <c r="I13">
-        <f>H13/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8666666666666671</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3498,26 +3352,28 @@
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="24">
         <v>28.5</v>
       </c>
-      <c r="D14" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="E14" s="26">
-        <v>30</v>
-      </c>
-      <c r="F14" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="G14" s="20">
+      <c r="D14" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="E14" s="24">
+        <v>30</v>
+      </c>
+      <c r="F14" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="G14" s="18">
         <v>118.3</v>
       </c>
       <c r="H14">
-        <f>G14/COUNTIF(C14:F14,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.574999999999999</v>
       </c>
       <c r="I14">
-        <f>H14/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8583333333333325</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3527,26 +3383,28 @@
       <c r="B15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="24">
         <v>29.2</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="24">
         <v>29</v>
       </c>
-      <c r="E15" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F15" s="26">
+      <c r="E15" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F15" s="24">
         <v>0</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="18">
         <v>88.1</v>
       </c>
       <c r="H15">
-        <f>G15/COUNTIF(C15:F15,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.366666666666664</v>
       </c>
       <c r="I15">
-        <f>H15/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7888888888888879</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3569,7 +3427,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -3612,26 +3470,28 @@
       <c r="B2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="24">
-        <v>29.9</v>
-      </c>
-      <c r="D2" s="24">
-        <v>30</v>
-      </c>
-      <c r="E2" s="24">
-        <v>30</v>
-      </c>
-      <c r="F2" s="24">
-        <v>30</v>
-      </c>
-      <c r="G2" s="25">
+      <c r="C2" s="22">
+        <v>29.9</v>
+      </c>
+      <c r="D2" s="22">
+        <v>30</v>
+      </c>
+      <c r="E2" s="22">
+        <v>30</v>
+      </c>
+      <c r="F2" s="22">
+        <v>30</v>
+      </c>
+      <c r="G2" s="23">
         <v>119.9</v>
       </c>
       <c r="H2">
-        <f>G2/COUNTIF(C2:F2,"&lt;&gt;0")</f>
+        <f t="shared" ref="H2:H15" si="0">G2/COUNTIF(C2:F2,"&lt;&gt;0")</f>
+        <v>29.975000000000001</v>
       </c>
       <c r="I2">
-        <f>H2/3</f>
+        <f t="shared" ref="I2:I15" si="1">H2/3</f>
+        <v>9.9916666666666671</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3641,26 +3501,28 @@
       <c r="B3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="D3" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="E3" s="26">
-        <v>30</v>
-      </c>
-      <c r="F3" s="26">
-        <v>30</v>
-      </c>
-      <c r="G3" s="20">
+      <c r="C3" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="D3" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="E3" s="24">
+        <v>30</v>
+      </c>
+      <c r="F3" s="24">
+        <v>30</v>
+      </c>
+      <c r="G3" s="18">
         <v>119.8</v>
       </c>
       <c r="H3">
-        <f>G3/COUNTIF(C3:F3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.95</v>
       </c>
       <c r="I3">
-        <f>H3/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9833333333333325</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3670,26 +3532,28 @@
       <c r="B4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="24">
         <v>29.6</v>
       </c>
-      <c r="D4" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="E4" s="26">
+      <c r="D4" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="E4" s="24">
         <v>29.8</v>
       </c>
-      <c r="F4" s="26">
-        <v>30</v>
-      </c>
-      <c r="G4" s="20">
+      <c r="F4" s="24">
+        <v>30</v>
+      </c>
+      <c r="G4" s="18">
         <v>119.3</v>
       </c>
       <c r="H4">
-        <f>G4/COUNTIF(C4:F4,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.824999999999999</v>
       </c>
       <c r="I4">
-        <f>H4/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9416666666666664</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3699,26 +3563,28 @@
       <c r="B5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="24">
         <v>29.4</v>
       </c>
-      <c r="D5" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="E5" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F5" s="26">
-        <v>30</v>
-      </c>
-      <c r="G5" s="20">
+      <c r="D5" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="E5" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F5" s="24">
+        <v>30</v>
+      </c>
+      <c r="G5" s="18">
         <v>119.2</v>
       </c>
       <c r="H5">
-        <f>G5/COUNTIF(C5:F5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.8</v>
       </c>
       <c r="I5">
-        <f>H5/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9333333333333336</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3728,26 +3594,28 @@
       <c r="B6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="24">
         <v>29.7</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="24">
         <v>29.5</v>
       </c>
-      <c r="E6" s="26">
-        <v>30</v>
-      </c>
-      <c r="F6" s="26">
-        <v>30</v>
-      </c>
-      <c r="G6" s="20">
+      <c r="E6" s="24">
+        <v>30</v>
+      </c>
+      <c r="F6" s="24">
+        <v>30</v>
+      </c>
+      <c r="G6" s="18">
         <v>119.2</v>
       </c>
       <c r="H6">
-        <f>G6/COUNTIF(C6:F6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.8</v>
       </c>
       <c r="I6">
-        <f>H6/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9333333333333336</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3757,26 +3625,28 @@
       <c r="B7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="24">
         <v>29.6</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="24">
         <v>29.8</v>
       </c>
-      <c r="E7" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F7" s="26">
+      <c r="E7" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F7" s="24">
         <v>29.8</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="18">
         <v>119.1</v>
       </c>
       <c r="H7">
-        <f>G7/COUNTIF(C7:F7,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.774999999999999</v>
       </c>
       <c r="I7">
-        <f>H7/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9249999999999989</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3786,26 +3656,28 @@
       <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="24">
         <v>29.2</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="24">
         <v>29.5</v>
       </c>
-      <c r="E8" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F8" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="G8" s="20">
+      <c r="E8" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F8" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="G8" s="18">
         <v>118.5</v>
       </c>
       <c r="H8">
-        <f>G8/COUNTIF(C8:F8,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.625</v>
       </c>
       <c r="I8">
-        <f>H8/3</f>
+        <f t="shared" si="1"/>
+        <v>9.875</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3815,26 +3687,28 @@
       <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="24">
         <v>29.2</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="24">
         <v>29.6</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="24">
         <v>29.7</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="24">
         <v>29.6</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="18">
         <v>118.1</v>
       </c>
       <c r="H9">
-        <f>G9/COUNTIF(C9:F9,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.524999999999999</v>
       </c>
       <c r="I9">
-        <f>H9/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8416666666666668</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3844,26 +3718,28 @@
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="24">
         <v>28.8</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="24">
         <v>29.5</v>
       </c>
-      <c r="E10" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F10" s="26">
+      <c r="E10" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F10" s="24">
         <v>29.7</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="18">
         <v>117.9</v>
       </c>
       <c r="H10">
-        <f>G10/COUNTIF(C10:F10,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.475000000000001</v>
       </c>
       <c r="I10">
-        <f>H10/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8250000000000011</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3873,26 +3749,28 @@
       <c r="B11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="24">
         <v>28.5</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="24">
         <v>29.5</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="24">
         <v>29.7</v>
       </c>
-      <c r="F11" s="26">
-        <v>30</v>
-      </c>
-      <c r="G11" s="20">
+      <c r="F11" s="24">
+        <v>30</v>
+      </c>
+      <c r="G11" s="18">
         <v>117.7</v>
       </c>
       <c r="H11">
-        <f>G11/COUNTIF(C11:F11,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.425000000000001</v>
       </c>
       <c r="I11">
-        <f>H11/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8083333333333336</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3902,26 +3780,28 @@
       <c r="B12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="24">
         <v>28.3</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="24">
         <v>29.3</v>
       </c>
-      <c r="E12" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F12" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="G12" s="20">
+      <c r="E12" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F12" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="G12" s="18">
         <v>117.4</v>
       </c>
       <c r="H12">
-        <f>G12/COUNTIF(C12:F12,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.35</v>
       </c>
       <c r="I12">
-        <f>H12/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7833333333333332</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3931,26 +3811,28 @@
       <c r="B13" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="24">
         <v>28.9</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="24">
         <v>29.4</v>
       </c>
-      <c r="E13" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="F13" s="26">
+      <c r="E13" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="F13" s="24">
         <v>29.2</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="18">
         <v>117.4</v>
       </c>
       <c r="H13">
-        <f>G13/COUNTIF(C13:F13,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.35</v>
       </c>
       <c r="I13">
-        <f>H13/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7833333333333332</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3960,26 +3842,28 @@
       <c r="B14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="24">
         <v>28.6</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="24">
         <v>29.5</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="24">
         <v>29.5</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="24">
         <v>29.7</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="18">
         <v>117.3</v>
       </c>
       <c r="H14">
-        <f>G14/COUNTIF(C14:F14,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.324999999999999</v>
       </c>
       <c r="I14">
-        <f>H14/3</f>
+        <f t="shared" si="1"/>
+        <v>9.7750000000000004</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3989,26 +3873,28 @@
       <c r="B15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="24">
         <v>29.4</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="24">
         <v>29.3</v>
       </c>
-      <c r="E15" s="26">
-        <v>30</v>
-      </c>
-      <c r="F15" s="26">
+      <c r="E15" s="24">
+        <v>30</v>
+      </c>
+      <c r="F15" s="24">
         <v>0</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="18">
         <v>88.7</v>
       </c>
       <c r="H15">
-        <f>G15/COUNTIF(C15:F15,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.566666666666666</v>
       </c>
       <c r="I15">
-        <f>H15/3</f>
+        <f t="shared" si="1"/>
+        <v>9.8555555555555561</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4031,7 +3917,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -4074,26 +3960,28 @@
       <c r="B2" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="24">
-        <v>30</v>
-      </c>
-      <c r="D2" s="24">
-        <v>30</v>
-      </c>
-      <c r="E2" s="24">
-        <v>30</v>
-      </c>
-      <c r="F2" s="24">
-        <v>30</v>
-      </c>
-      <c r="G2" s="25">
+      <c r="C2" s="22">
+        <v>30</v>
+      </c>
+      <c r="D2" s="22">
+        <v>30</v>
+      </c>
+      <c r="E2" s="22">
+        <v>30</v>
+      </c>
+      <c r="F2" s="22">
+        <v>30</v>
+      </c>
+      <c r="G2" s="23">
         <v>120</v>
       </c>
       <c r="H2">
-        <f>G2/COUNTIF(C2:F2,"&lt;&gt;0")</f>
+        <f t="shared" ref="H2:H15" si="0">G2/COUNTIF(C2:F2,"&lt;&gt;0")</f>
+        <v>30</v>
       </c>
       <c r="I2">
-        <f>H2/3</f>
+        <f t="shared" ref="I2:I15" si="1">H2/3</f>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4101,26 +3989,28 @@
       <c r="B3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="26">
-        <v>30</v>
-      </c>
-      <c r="D3" s="26">
-        <v>30</v>
-      </c>
-      <c r="E3" s="26">
-        <v>30</v>
-      </c>
-      <c r="F3" s="26">
-        <v>30</v>
-      </c>
-      <c r="G3" s="20">
+      <c r="C3" s="24">
+        <v>30</v>
+      </c>
+      <c r="D3" s="24">
+        <v>30</v>
+      </c>
+      <c r="E3" s="24">
+        <v>30</v>
+      </c>
+      <c r="F3" s="24">
+        <v>30</v>
+      </c>
+      <c r="G3" s="18">
         <v>120</v>
       </c>
       <c r="H3">
-        <f>G3/COUNTIF(C3:F3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="I3">
-        <f>H3/3</f>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4128,26 +4018,28 @@
       <c r="B4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="26">
-        <v>30</v>
-      </c>
-      <c r="D4" s="26">
-        <v>30</v>
-      </c>
-      <c r="E4" s="26">
-        <v>30</v>
-      </c>
-      <c r="F4" s="26">
-        <v>30</v>
-      </c>
-      <c r="G4" s="20">
+      <c r="C4" s="24">
+        <v>30</v>
+      </c>
+      <c r="D4" s="24">
+        <v>30</v>
+      </c>
+      <c r="E4" s="24">
+        <v>30</v>
+      </c>
+      <c r="F4" s="24">
+        <v>30</v>
+      </c>
+      <c r="G4" s="18">
         <v>120</v>
       </c>
       <c r="H4">
-        <f>G4/COUNTIF(C4:F4,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="I4">
-        <f>H4/3</f>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4157,26 +4049,28 @@
       <c r="B5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="26">
-        <v>30</v>
-      </c>
-      <c r="D5" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="E5" s="26">
-        <v>30</v>
-      </c>
-      <c r="F5" s="26">
-        <v>30</v>
-      </c>
-      <c r="G5" s="20">
+      <c r="C5" s="24">
+        <v>30</v>
+      </c>
+      <c r="D5" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="E5" s="24">
+        <v>30</v>
+      </c>
+      <c r="F5" s="24">
+        <v>30</v>
+      </c>
+      <c r="G5" s="18">
         <v>119.9</v>
       </c>
       <c r="H5">
-        <f>G5/COUNTIF(C5:F5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.975000000000001</v>
       </c>
       <c r="I5">
-        <f>H5/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9916666666666671</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4186,26 +4080,28 @@
       <c r="B6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="24">
         <v>29.8</v>
       </c>
-      <c r="D6" s="26">
-        <v>30</v>
-      </c>
-      <c r="E6" s="26">
-        <v>30</v>
-      </c>
-      <c r="F6" s="26">
-        <v>30</v>
-      </c>
-      <c r="G6" s="20">
+      <c r="D6" s="24">
+        <v>30</v>
+      </c>
+      <c r="E6" s="24">
+        <v>30</v>
+      </c>
+      <c r="F6" s="24">
+        <v>30</v>
+      </c>
+      <c r="G6" s="18">
         <v>119.8</v>
       </c>
       <c r="H6">
-        <f>G6/COUNTIF(C6:F6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.95</v>
       </c>
       <c r="I6">
-        <f>H6/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9833333333333325</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4215,26 +4111,28 @@
       <c r="B7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="D7" s="26">
+      <c r="C7" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="D7" s="24">
         <v>29.7</v>
       </c>
-      <c r="E7" s="26">
-        <v>30</v>
-      </c>
-      <c r="F7" s="26">
-        <v>30</v>
-      </c>
-      <c r="G7" s="20">
+      <c r="E7" s="24">
+        <v>30</v>
+      </c>
+      <c r="F7" s="24">
+        <v>30</v>
+      </c>
+      <c r="G7" s="18">
         <v>119.6</v>
       </c>
       <c r="H7">
-        <f>G7/COUNTIF(C7:F7,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.9</v>
       </c>
       <c r="I7">
-        <f>H7/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9666666666666668</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4244,26 +4142,28 @@
       <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="26">
-        <v>30</v>
-      </c>
-      <c r="D8" s="26">
+      <c r="C8" s="24">
+        <v>30</v>
+      </c>
+      <c r="D8" s="24">
         <v>29.6</v>
       </c>
-      <c r="E8" s="26">
-        <v>30</v>
-      </c>
-      <c r="F8" s="26">
-        <v>30</v>
-      </c>
-      <c r="G8" s="20">
+      <c r="E8" s="24">
+        <v>30</v>
+      </c>
+      <c r="F8" s="24">
+        <v>30</v>
+      </c>
+      <c r="G8" s="18">
         <v>119.6</v>
       </c>
       <c r="H8">
-        <f>G8/COUNTIF(C8:F8,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.9</v>
       </c>
       <c r="I8">
-        <f>H8/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9666666666666668</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4273,26 +4173,28 @@
       <c r="B9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="24">
         <v>29.8</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="24">
         <v>29.7</v>
       </c>
-      <c r="E9" s="26">
-        <v>30</v>
-      </c>
-      <c r="F9" s="26">
-        <v>30</v>
-      </c>
-      <c r="G9" s="20">
+      <c r="E9" s="24">
+        <v>30</v>
+      </c>
+      <c r="F9" s="24">
+        <v>30</v>
+      </c>
+      <c r="G9" s="18">
         <v>119.5</v>
       </c>
       <c r="H9">
-        <f>G9/COUNTIF(C9:F9,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.875</v>
       </c>
       <c r="I9">
-        <f>H9/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9583333333333339</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4302,26 +4204,28 @@
       <c r="B10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="D10" s="26">
+      <c r="C10" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="D10" s="24">
         <v>29.6</v>
       </c>
-      <c r="E10" s="26">
-        <v>30</v>
-      </c>
-      <c r="F10" s="26">
-        <v>30</v>
-      </c>
-      <c r="G10" s="20">
+      <c r="E10" s="24">
+        <v>30</v>
+      </c>
+      <c r="F10" s="24">
+        <v>30</v>
+      </c>
+      <c r="G10" s="18">
         <v>119.5</v>
       </c>
       <c r="H10">
-        <f>G10/COUNTIF(C10:F10,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.875</v>
       </c>
       <c r="I10">
-        <f>H10/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9583333333333339</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4331,26 +4235,28 @@
       <c r="B11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="24">
         <v>29.4</v>
       </c>
-      <c r="D11" s="26">
-        <v>30</v>
-      </c>
-      <c r="E11" s="26">
-        <v>30</v>
-      </c>
-      <c r="F11" s="26">
-        <v>30</v>
-      </c>
-      <c r="G11" s="20">
+      <c r="D11" s="24">
+        <v>30</v>
+      </c>
+      <c r="E11" s="24">
+        <v>30</v>
+      </c>
+      <c r="F11" s="24">
+        <v>30</v>
+      </c>
+      <c r="G11" s="18">
         <v>119.4</v>
       </c>
       <c r="H11">
-        <f>G11/COUNTIF(C11:F11,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.85</v>
       </c>
       <c r="I11">
-        <f>H11/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9500000000000011</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4360,26 +4266,28 @@
       <c r="B12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="26">
-        <v>30</v>
-      </c>
-      <c r="D12" s="26">
+      <c r="C12" s="24">
+        <v>30</v>
+      </c>
+      <c r="D12" s="24">
         <v>29.4</v>
       </c>
-      <c r="E12" s="26">
-        <v>30</v>
-      </c>
-      <c r="F12" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="G12" s="20">
+      <c r="E12" s="24">
+        <v>30</v>
+      </c>
+      <c r="F12" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="G12" s="18">
         <v>119.3</v>
       </c>
       <c r="H12">
-        <f>G12/COUNTIF(C12:F12,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.824999999999999</v>
       </c>
       <c r="I12">
-        <f>H12/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9416666666666664</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4389,26 +4297,28 @@
       <c r="B13" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="26">
-        <v>29.9</v>
-      </c>
-      <c r="D13" s="26">
+      <c r="C13" s="24">
+        <v>29.9</v>
+      </c>
+      <c r="D13" s="24">
         <v>29.6</v>
       </c>
-      <c r="E13" s="26">
-        <v>30</v>
-      </c>
-      <c r="F13" s="26">
+      <c r="E13" s="24">
+        <v>30</v>
+      </c>
+      <c r="F13" s="24">
         <v>29.8</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="18">
         <v>119.3</v>
       </c>
       <c r="H13">
-        <f>G13/COUNTIF(C13:F13,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.824999999999999</v>
       </c>
       <c r="I13">
-        <f>H13/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9416666666666664</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4418,26 +4328,28 @@
       <c r="B14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="24">
         <v>29.5</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="24">
         <v>29</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="24">
         <v>29.7</v>
       </c>
-      <c r="F14" s="26">
-        <v>30</v>
-      </c>
-      <c r="G14" s="20">
+      <c r="F14" s="24">
+        <v>30</v>
+      </c>
+      <c r="G14" s="18">
         <v>118.2</v>
       </c>
       <c r="H14">
-        <f>G14/COUNTIF(C14:F14,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.55</v>
       </c>
       <c r="I14">
-        <f>H14/3</f>
+        <f t="shared" si="1"/>
+        <v>9.85</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4447,26 +4359,28 @@
       <c r="B15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="24">
         <v>29.7</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="24">
         <v>29.6</v>
       </c>
-      <c r="E15" s="26">
-        <v>30</v>
-      </c>
-      <c r="F15" s="26">
+      <c r="E15" s="24">
+        <v>30</v>
+      </c>
+      <c r="F15" s="24">
         <v>0</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="18">
         <v>89.3</v>
       </c>
       <c r="H15">
-        <f>G15/COUNTIF(C15:F15,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>29.766666666666666</v>
       </c>
       <c r="I15">
-        <f>H15/3</f>
+        <f t="shared" si="1"/>
+        <v>9.9222222222222225</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
